--- a/output/pdf_financials_xlsx/OM.xlsx
+++ b/output/pdf_financials_xlsx/OM.xlsx
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2.086139</v>
+        <v>-2.086139</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.245425</v>
+        <v>-1.245425</v>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>20.288</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>21.425</v>
+        <v>-21.425</v>
       </c>
     </row>
     <row r="17">
@@ -1410,13 +1410,13 @@
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0.455822</v>
+        <v>-6.207684</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-1.950985</v>
+        <v>-10.127453</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-2.110322</v>
+        <v>-16.650936</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>-0.7188099999999999</v>
@@ -1605,10 +1605,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2.086139</v>
+        <v>-2.086139</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.245425</v>
+        <v>-1.245425</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
@@ -1636,16 +1636,16 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2.875931</v>
+        <v>-2.875931</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.088234</v>
+        <v>-4.088234</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>7.270307</v>
+        <v>-7.270307</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>5.253499</v>
+        <v>-5.253499</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-18.568628</v>
@@ -1657,7 +1657,7 @@
         <v>21.425</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>21.425</v>
+        <v>-21.425</v>
       </c>
     </row>
     <row r="21">
@@ -1791,10 +1791,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2.086139</v>
+        <v>-2.086139</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.245425</v>
+        <v>-1.245425</v>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
@@ -1822,16 +1822,16 @@
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.875931</v>
+        <v>-2.875931</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>4.088234</v>
+        <v>-4.088234</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>7.270307</v>
+        <v>-7.270307</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>5.253499</v>
+        <v>-5.253499</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-18.568628</v>
@@ -1843,7 +1843,7 @@
         <v>21.425</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>21.425</v>
+        <v>-21.425</v>
       </c>
     </row>
     <row r="24">
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-45.350848</v>
+        <v>45.350848</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-49.817</v>
+        <v>49.817</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -2012,16 +2012,16 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-47.932183</v>
+        <v>47.932183</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-102.20585</v>
+        <v>102.20585</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-145.40614</v>
+        <v>145.40614</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-175.116633</v>
+        <v>175.116633</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>206.318089</v>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.086139</v>
+        <v>-2.086139</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.245425</v>
+        <v>-1.245425</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>20.728</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>21.425</v>
+        <v>-21.425</v>
       </c>
     </row>
     <row r="28">
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2.086139</v>
+        <v>-2.086139</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.245425</v>
+        <v>-1.245425</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>20.728</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>21.425</v>
+        <v>-21.425</v>
       </c>
     </row>
     <row r="30">
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
@@ -2344,13 +2344,13 @@
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>13.68114623142832</v>
+        <v>186.3188537685717</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>32.30525337796162</v>
+        <v>167.6947466220384</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>22.49659377851954</v>
+        <v>177.5034062214805</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>12.035713490377</v>
@@ -2365,7 +2365,7 @@
         <v>5.60429810725552</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -6553,7 +6553,7 @@
         <v>-18.568628</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>11.271856</v>
+        <v>-11.271856</v>
       </c>
       <c r="O99" s="3" t="n">
         <v>-21.425</v>
@@ -25959,7 +25959,7 @@
         <v>-18.568628</v>
       </c>
       <c r="Q190" s="5" t="n">
-        <v>11.271856</v>
+        <v>-11.271856</v>
       </c>
       <c r="R190" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         </is>
       </c>
       <c r="S327" s="5" t="n">
-        <v>21.425</v>
+        <v>-21.425</v>
       </c>
     </row>
     <row r="328">
@@ -44049,10 +44049,10 @@
         </is>
       </c>
       <c r="O390" s="5" t="n">
-        <v>5.253499</v>
+        <v>-5.253499</v>
       </c>
       <c r="P390" s="5" t="n">
-        <v>18.568628</v>
+        <v>-18.568628</v>
       </c>
       <c r="Q390" t="inlineStr">
         <is>
@@ -45115,10 +45115,10 @@
         </is>
       </c>
       <c r="M402" s="5" t="n">
-        <v>4.088234</v>
+        <v>-4.088234</v>
       </c>
       <c r="N402" s="5" t="n">
-        <v>7.270307</v>
+        <v>-7.270307</v>
       </c>
       <c r="O402" t="inlineStr">
         <is>
@@ -46204,10 +46204,10 @@
         </is>
       </c>
       <c r="L414" s="5" t="n">
-        <v>2.875931</v>
+        <v>-2.875931</v>
       </c>
       <c r="M414" s="5" t="n">
-        <v>4.088234</v>
+        <v>-4.088234</v>
       </c>
       <c r="N414" t="inlineStr">
         <is>
@@ -46570,10 +46570,10 @@
         </is>
       </c>
       <c r="L418" s="5" t="n">
-        <v>1.991345</v>
+        <v>-1.991345</v>
       </c>
       <c r="M418" s="5" t="n">
-        <v>4.088234</v>
+        <v>-4.088234</v>
       </c>
       <c r="N418" t="inlineStr">
         <is>
@@ -48778,10 +48778,10 @@
         </is>
       </c>
       <c r="E443" s="5" t="n">
-        <v>2.086139</v>
+        <v>-2.086139</v>
       </c>
       <c r="F443" s="5" t="n">
-        <v>1.245425</v>
+        <v>-1.245425</v>
       </c>
       <c r="G443" t="inlineStr">
         <is>
@@ -49053,10 +49053,10 @@
         </is>
       </c>
       <c r="E446" s="5" t="n">
-        <v>2.081139</v>
+        <v>-2.081139</v>
       </c>
       <c r="F446" s="5" t="n">
-        <v>1.270425</v>
+        <v>-1.270425</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/OM.xlsx
+++ b/output/pdf_financials_xlsx/OM.xlsx
@@ -2501,7 +2501,7 @@
         <v>8.453161</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.507997</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>6.469732</v>
@@ -2510,13 +2510,13 @@
         <v>3.078856</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.67061</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>101.656</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>79.791</v>
       </c>
     </row>
     <row r="35">
@@ -2625,7 +2625,7 @@
         <v>8.453161</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.507997</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>6.469732</v>
@@ -2634,13 +2634,13 @@
         <v>3.078856</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.67061</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>1.929</v>
+        <v>103.585</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>3.508</v>
+        <v>83.29900000000001</v>
       </c>
     </row>
     <row r="37">
@@ -3369,7 +3369,7 @@
         <v>11.030023</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.183608</v>
+        <v>0.675611</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.085213</v>
@@ -3378,13 +3378,13 @@
         <v>1.378235</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.759058</v>
+        <v>0.088448</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>102.308</v>
+        <v>0.652</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>85.753</v>
+        <v>5.962</v>
       </c>
     </row>
     <row r="49">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -36959,7 +36959,11 @@
           <t>General and administration expenses (note 16) 3,903</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -39612,7 +39616,11 @@
           <t>General and administration expenses (note 13)</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/OM.xlsx
+++ b/output/pdf_financials_xlsx/OM.xlsx
@@ -1183,7 +1183,7 @@
         <v>-0</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-0</v>
+        <v>-15.554</v>
       </c>
     </row>
     <row r="14">
@@ -2097,7 +2097,7 @@
         <v>20.728</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-21.425</v>
+        <v>-5.871</v>
       </c>
     </row>
     <row r="28">
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.005886</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.005508</v>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.086139</v>
+        <v>-2.080253</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.245425</v>
+        <v>-1.239917</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>20.728</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-21.425</v>
+        <v>-5.871</v>
       </c>
     </row>
     <row r="30">
@@ -6569,10 +6569,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.005886</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.005508</v>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
@@ -34963,7 +34963,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E290" s="5" t="n">
         <v>0.005886</v>
       </c>
@@ -37879,7 +37883,11 @@
           <t>Net finance expense 41,398</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -47967,7 +47975,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E434" s="5" t="n">
         <v>0.005886</v>
       </c>
